--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日程" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10月1日" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10月2日" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10月5日" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10月6日" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="一日目" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="二日目" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="三日目" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四日目" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出演者と支度" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
@@ -516,14 +516,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>全八本 137カット ／ 撮影 四日 ／ 日付はすべて仮</t>
+          <t>全八本 137カット ／ 撮影 四日 ／ 日付は10月中で未定</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>日付</t>
+          <t>日</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10月1日（木）</t>
+          <t>一日目</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -578,7 +578,7 @@
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10月2日（金）</t>
+          <t>二日目</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10月5日（月）</t>
+          <t>三日目</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10月6日（火）</t>
+          <t>四日目</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>2026年10月1日（木）　※仮</t>
+          <t>一日目　── 10月中（日にちは未定）</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>2026年10月2日（金）　※仮</t>
+          <t>二日目　── 10月中（日にちは未定）</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>2026年10月5日（月）　※仮</t>
+          <t>三日目　── 10月中（日にちは未定）</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>2026年10月6日（火）　※仮</t>
+          <t>四日目　── 10月中（日にちは未定）</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>出演者と衣装・鞄 四色ぶんが揃ってから。永尾さんの車も要る（②の合図）。曇りの日に合わせる。予備日は10月7日（水）。</t>
+          <t>出演者と衣装・鞄 四色ぶんが揃ってから。永尾さんの車も要る（②の合図）。曇りの日に合わせる。予備日を一日とる。</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2カット（3枚目は10月1日に撮る）</t>
+          <t>2カット（3枚目は一日目に撮る）</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>10月6日</t>
+          <t>四日目</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>10月6日</t>
+          <t>四日目</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>10月1日</t>
+          <t>一日目</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>10月2日</t>
+          <t>二日目</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>10月1日・10月5日</t>
+          <t>一日目・三日目</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -3263,7 +3263,7 @@
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>ふだんの仕事着。
-永尾社長・くさがやさんは10月1日、佐藤さんは10月5日。</t>
+永尾社長・くさがやさんは一日目、佐藤さんは三日目。</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -1802,7 +1802,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>ブルックリンの品を作っている日に合わせる。佐藤さんに製作日を確認してから決める。</t>
+          <t>佐藤さんの休日に合わせる。工房は止まっているので、機械は佐藤さんに動かしてもらう。他の人が映る画は撮れない。</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       <c r="D9" s="5" t="inlineStr">
         <is>
           <t>⑥ S1 工房の全体
-1枚目 工房の全体（広角の引き・固定）→ 2枚目 機械の並び（横から・人は引きの中に小さく）→ 3枚目 作業台の手元（寄り）。</t>
+1枚目 工房の全体（広角の引き・固定）→ 2枚目 機械の並び（横から・佐藤さんが引きの中に小さく）→ 3枚目 作業台の手元（寄り）。</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1893,7 +1893,7 @@
       <c r="D10" s="5" t="inlineStr">
         <is>
           <t>⑥ S2 機械と材料
-1枚目 材料の壁（正面）→ 2枚目 機械と人（人は引きの中に小さく）→ 3枚目 佐藤さんの引き。</t>
+1枚目 材料の壁（正面）→ 2枚目 機械と人（佐藤さんが引きの中に小さく）→ 3枚目 佐藤さんの引き。</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -2408,7 +2408,7 @@
       <c r="D25" s="5" t="inlineStr">
         <is>
           <t>⑥ S8 梱包
-1枚目 包む手元（寄り）→ 2枚目 梱包場の引き（奥にも人）→ 3枚目 佐藤さんのバストショット。</t>
+1枚目 包む手元（寄り）→ 2枚目 梱包場の引き（休日なので人は一人。奥は空けたまま撮る）→ 3枚目 佐藤さんのバストショット。</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -1616,7 +1616,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>職人（手だけ）
+          <t>くさがやさん（手だけ）
 刃、道具、革</t>
         </is>
       </c>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>職人（手だけ）
+          <t>くさがやさん（手だけ）
 コバ塗料、道具、断面</t>
         </is>
       </c>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>手だけ（時計・指輪は外す）
+          <t>くさがやさん（手だけ・時計と指輪は外す）
 革 二枚、染料、道具</t>
         </is>
       </c>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>手だけ
+          <t>くさがやさん（手と肩）
 革</t>
         </is>
       </c>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>手だけ（白手袋）
+          <t>くさがやさん（手だけ・白手袋）
 金具</t>
         </is>
       </c>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>―
+          <t>佐藤さん（シルエット・1枚目だけ）
 完成品、工房の道具、ロゴ</t>
         </is>
       </c>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>職人（手だけ）
+          <t>佐藤さん（手だけ）
 抜き型、革、裁断機</t>
         </is>
       </c>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>職人（手だけ）
+          <t>佐藤さん（手だけ）
 革 二枚、型</t>
         </is>
       </c>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>職人（手と上半身）
+          <t>佐藤さん（手と上半身）
 ミシン、糸、革</t>
         </is>
       </c>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>職人（手と上半身）
+          <t>佐藤さん（手と上半身）
 木槌、道具、立ち上がった鞄</t>
         </is>
       </c>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>職人（手だけ）
+          <t>佐藤さん（手だけ）
 完成した鞄、ロゴ</t>
         </is>
       </c>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>全八本 139カット ／ 撮影 四日 ／ 日付は10月中で未定</t>
+          <t>全八本 139カット ／ 撮影 五日 ／ 日付は10月中で未定</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>9:00〜14:00</t>
+          <t>9:00〜14:15</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>9:00〜15:25</t>
+          <t>9:00〜16:25</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>9:30〜14:30</t>
+          <t>9:30〜14:55</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>9:30〜14:30</t>
+          <t>9:30〜14:50</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>9:00〜16:20</t>
+          <t>9:00〜17:05</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>9:00〜14:00</t>
+          <t>9:00〜14:15</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
     <row r="12" ht="39" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>10:55〜11:10</t>
+          <t>10:55〜11:13</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -948,7 +948,7 @@
     <row r="13" ht="39" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>11:10〜11:25</t>
+          <t>11:13〜11:30</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -982,7 +982,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>11:25〜12:25</t>
+          <t>11:30〜12:30</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -1010,7 +1010,7 @@
     <row r="15" ht="39" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>12:25〜12:45</t>
+          <t>12:30〜12:52</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="16" ht="39" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>12:45〜13:05</t>
+          <t>12:52〜13:14</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>13:05〜13:25</t>
+          <t>13:14〜13:36</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="18" ht="39" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>13:25〜13:40</t>
+          <t>13:36〜13:53</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="19" ht="39" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>13:40〜14:00</t>
+          <t>13:53〜14:15</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>9:00〜15:25</t>
+          <t>9:00〜16:25</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
     <row r="9" ht="39" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>9:00〜9:20</t>
+          <t>9:00〜9:26</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1337,7 +1337,7 @@
     <row r="10" ht="39" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>9:20〜9:35</t>
+          <t>9:26〜9:45</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="11" ht="39" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>9:35〜9:55</t>
+          <t>9:45〜10:10</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1405,7 +1405,7 @@
     <row r="12" ht="39" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>10:10〜10:35</t>
+          <t>10:25〜11:00</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1440,7 +1440,7 @@
     <row r="13" ht="39" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>10:35〜10:50</t>
+          <t>11:00〜11:21</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1474,7 +1474,7 @@
     <row r="14" ht="39" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>10:50〜11:00</t>
+          <t>11:21〜11:35</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1508,7 +1508,7 @@
     <row r="15" ht="39" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>11:10〜11:40</t>
+          <t>11:45〜12:20</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1543,7 +1543,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>11:40〜12:30</t>
+          <t>12:20〜13:10</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1571,7 +1571,7 @@
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>12:30〜12:45</t>
+          <t>13:10〜13:25</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1606,7 +1606,7 @@
     <row r="18" ht="39" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:45〜13:15</t>
+          <t>13:25〜13:58</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="19" ht="39" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>13:15〜13:35</t>
+          <t>13:58〜14:20</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1675,7 +1675,7 @@
     <row r="20" ht="39" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>13:35〜13:55</t>
+          <t>14:20〜14:43</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -1710,7 +1710,7 @@
     <row r="21" ht="39" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>13:55〜14:15</t>
+          <t>14:43〜15:06</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1744,7 +1744,7 @@
     <row r="22" ht="39" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>14:15〜14:40</t>
+          <t>15:06〜15:34</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -1778,7 +1778,7 @@
     <row r="23" ht="39" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>14:40〜15:00</t>
+          <t>15:34〜15:57</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1812,7 +1812,7 @@
     <row r="24" ht="39" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>15:00〜15:25</t>
+          <t>15:57〜16:25</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>9:30〜14:30</t>
+          <t>9:30〜14:55</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
     <row r="11" ht="39" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10:10〜10:40</t>
+          <t>10:10〜10:45</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -2073,7 +2073,7 @@
     <row r="12" ht="39" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>10:40〜11:10</t>
+          <t>10:45〜11:20</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -2108,7 +2108,7 @@
     <row r="13" ht="39" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>11:10〜11:50</t>
+          <t>11:20〜12:05</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -2142,7 +2142,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>11:50〜12:50</t>
+          <t>12:05〜13:05</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -2174,7 +2174,7 @@
     <row r="15" ht="39" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>12:50〜13:30</t>
+          <t>13:05〜13:50</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -2209,7 +2209,7 @@
     <row r="16" ht="39" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>13:30〜14:00</t>
+          <t>13:50〜14:25</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -2244,7 +2244,7 @@
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>14:00〜14:30</t>
+          <t>14:25〜14:55</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>9:30〜14:30</t>
+          <t>9:30〜14:50</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
     <row r="10" ht="39" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>9:50〜10:20</t>
+          <t>9:50〜10:25</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -2471,7 +2471,7 @@
     <row r="11" ht="39" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10:20〜10:45</t>
+          <t>10:25〜10:50</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -2506,7 +2506,7 @@
     <row r="12" ht="39" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>10:45〜11:25</t>
+          <t>10:50〜11:35</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -2541,7 +2541,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>11:25〜12:25</t>
+          <t>11:35〜12:35</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -2569,7 +2569,7 @@
     <row r="14" ht="39" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>12:25〜12:50</t>
+          <t>12:35〜13:06</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="15" ht="39" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>12:50〜13:05</t>
+          <t>13:06〜13:25</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -2638,7 +2638,7 @@
     <row r="16" ht="39" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>13:15〜13:45</t>
+          <t>13:35〜14:05</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -2671,7 +2671,7 @@
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>14:00〜14:30</t>
+          <t>14:20〜14:50</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>9:00〜16:20</t>
+          <t>9:00〜17:05</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
     <row r="9" ht="39" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>9:00〜9:35</t>
+          <t>9:00〜9:41</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -2857,7 +2857,7 @@
     <row r="10" ht="39" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>9:35〜10:00</t>
+          <t>9:41〜10:10</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -2891,7 +2891,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>10:00〜11:00</t>
+          <t>10:10〜11:10</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -2919,7 +2919,7 @@
     <row r="12" ht="39" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>11:00〜11:20</t>
+          <t>11:10〜11:34</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -2954,7 +2954,7 @@
     <row r="13" ht="39" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>11:20〜11:40</t>
+          <t>11:34〜11:58</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -2988,7 +2988,7 @@
     <row r="14" ht="39" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>11:40〜11:55</t>
+          <t>11:58〜12:16</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -3022,7 +3022,7 @@
     <row r="15" ht="39" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>11:55〜12:10</t>
+          <t>12:16〜12:35</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -3056,7 +3056,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>12:10〜13:10</t>
+          <t>12:35〜13:35</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -3081,14 +3081,14 @@
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>出演者の拘束は 9:00〜15:25。</t>
+          <t>出演者の拘束は 9:00〜16:05。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>13:10〜13:30</t>
+          <t>13:35〜14:00</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -3123,7 +3123,7 @@
     <row r="18" ht="39" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>13:30〜13:50</t>
+          <t>14:00〜14:25</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -3157,7 +3157,7 @@
     <row r="19" ht="39" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>14:35〜14:55</t>
+          <t>15:10〜15:35</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -3192,7 +3192,7 @@
     <row r="20" ht="39" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>14:55〜15:25</t>
+          <t>15:35〜16:05</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -3225,7 +3225,7 @@
     <row r="21" ht="39" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>15:35〜16:00</t>
+          <t>16:15〜16:43</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -3260,7 +3260,7 @@
     <row r="22" ht="39" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>16:00〜16:20</t>
+          <t>16:43〜17:05</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -827,7 +827,7 @@
       <c r="C9" s="10" t="inlineStr">
         <is>
           <t>永尾社長
-椅子、ピンマイク</t>
+椅子、レコーダー</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -856,7 +856,7 @@
       <c r="C10" s="10" t="inlineStr">
         <is>
           <t>くさがやさん
-椅子、ピンマイク</t>
+椅子、レコーダー</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -2682,7 +2682,7 @@
       <c r="C17" s="10" t="inlineStr">
         <is>
           <t>佐藤さん
-椅子、ピンマイク</t>
+椅子、レコーダー</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>9:00〜14:15</t>
+          <t>9:00〜13:40</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -597,12 +597,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>9:00〜16:25</t>
+          <t>9:00〜16:07</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>44カット</t>
+          <t>41カット</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>21カット</t>
+          <t>24カット</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>9:00〜14:15</t>
+          <t>9:00〜13:40</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="11" ht="39" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10:15〜10:45</t>
+          <t>10:15〜10:40</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>机は一度組んで、企画のシーンを続けて。
+          <t>企画から設計まで、続けて撮る。机は一度組んだら動かさない。
 3カット</t>
         </is>
       </c>
@@ -913,268 +913,268 @@
     <row r="12" ht="39" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>10:55〜11:13</t>
+          <t>10:40〜11:00</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
+          <t>同じ（企画から続けて）</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>手だけ
+図面、型紙</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>⑤ S3 設計
+1枚目 図面をなぞる手（寄り）→ 2枚目 型紙の俯瞰 → 3枚目 机の引き。</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>9秒</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>3カット</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="39" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>11:10〜11:22</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
           <t>事務所の机（正面固定）</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>出演者（手と肩だけ）
 鞄、机</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>⑦ S1 机の上の鞄
 1枚目 机の上の鞄（正面固定の引き）→ 2枚目 同じ画角のまま → 3枚目 口を開ける。</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>7秒</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>十四カット全部が同じ画角。
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>五シーンを切らずに、頭から終わりまで一度で通す。三テイク。
 3カット</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="39" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>11:13〜11:30</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>同じ</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
+    <row r="14" ht="39" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>11:22〜11:34</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>同じ（通しの続き）</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>出演者（手だけ）
+A4書類、13インチPC</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>⑦ S2 書類とPCを入れる
+1枚目 A4書類を入れる → 2枚目 ノートPCが底まで収まる → 3枚目 手帳・鍵・サングラス。同じ画角。</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>8秒</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>3カット</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="39" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>11:34〜11:46</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>同じ（通しの続き）</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>出演者（手だけ）
+手帳、鍵、サングラス、ペン、傘、水筒</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>⑦ S3 小物を入れる
+1枚目 ペン・小物 → 2枚目 傘・水筒 → 3枚目 最後の一つで手が止まる。</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>8秒</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>3カット</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="39" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>11:46〜11:58</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>同じ（通しの続き）</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>出演者（手と肩だけ）
 鞄</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>⑦ S4 持って出る
 1枚目 持ち上げる → 2枚目 肩に掛けてフレームの外へ出ていく。</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>5秒</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>2カット</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>11:30〜12:30</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
+    <row r="17" ht="39" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>11:58〜12:10</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>同じ（通しの続き）</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>―
+何も乗っていない机、ロゴ</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>⑦ S5 机だけが残る
+1枚目 何も乗っていない机だけが残る → 2枚目 テロップを重ねる → 3枚目 ロゴ。</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>7秒</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>3カット</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>12:10〜13:10</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>昼休み</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>1時間0分</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15" ht="39" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>12:30〜12:52</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19" ht="39" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>13:10〜13:40</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>店内 → ショーウィンドウ越し</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>―
 店内の商品、ショーウィンドウ</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>⑤ S5 店舗
 1枚目 店内の引き → 2枚目 ショーウィンドウ越し。</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>11秒</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>人が映らないカット。まとめて撮る。
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>人が映らないカット。
 2カット</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="39" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>12:52〜13:14</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>同じ</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>手だけ
-図面、型紙</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>⑤ S3 設計
-1枚目 図面をなぞる手（寄り）→ 2枚目 型紙の俯瞰 → 3枚目 机の引き。</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>9秒</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>3カット</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="39" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>13:14〜13:36</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>同じ</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>出演者（手だけ）
-A4書類、13インチPC</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>⑦ S2 書類とPCを入れる
-1枚目 A4書類を入れる → 2枚目 ノートPCが底まで収まる → 3枚目 手帳・鍵・サングラス。同じ画角。</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>8秒</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>3カット</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="39" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>13:36〜13:53</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>同じ</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>出演者（手だけ）
-手帳、鍵、サングラス、ペン、傘、水筒</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>⑦ S3 小物を入れる
-1枚目 ペン・小物 → 2枚目 傘・水筒 → 3枚目 最後の一つで手が止まる。</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>8秒</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>3カット</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="39" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>13:53〜14:15</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>同じ</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>―
-何も乗っていない机、ロゴ</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>⑦ S5 机だけが残る
-1枚目 何も乗っていない机だけが残る → 2枚目 テロップを重ねる → 3枚目 ロゴ。</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>7秒</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>3カット</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>9:00〜16:25</t>
+          <t>9:00〜16:07</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
     <row r="9" ht="39" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>9:00〜9:26</t>
+          <t>9:00〜9:25</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1330,14 +1330,15 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>3カット</t>
+          <t>つかみと見送りは同じ立ち位置。設営は一度。
+3カット</t>
         </is>
       </c>
     </row>
     <row r="10" ht="39" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>9:26〜9:45</t>
+          <t>9:25〜9:45</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1371,7 +1372,7 @@
     <row r="11" ht="39" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>9:45〜10:10</t>
+          <t>9:55〜10:20</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1398,152 +1399,153 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>3カット</t>
+          <t>使っている場面。外で動いてもらって、体をほぐす。
+3カット</t>
         </is>
       </c>
     </row>
     <row r="12" ht="39" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>10:25〜11:00</t>
+          <t>10:30〜11:05</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
+          <t>店内のレジまわり → 店の前の街</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>くさがやさん、購入者
+商品、ノートPC</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>⑤ S6 購入・使う
+1枚目 会計の引き → 2枚目 手渡しと笑顔 → 3枚目 使っている手元。</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>7秒</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>会計から使う場面まで。ここまでで、話す前にカメラに慣れてもらう。
+3カット</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="39" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>11:15〜11:50</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
           <t>店舗の窓辺。窓を横に、手前に植物を置く</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>購入者
 商品、手前に置く植物</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>⑧ S3 話しはじめる
 1枚目 バストショット（手前に植物を置いてボカす）→ 2枚目 Bロールの引き → 3枚目 商品の寄り。</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>8秒</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>三シーン続けて。カメラは動かさない。
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>ここからインタビュー。三シーン続けて。カメラは動かさない。購入者はここまで。
 3カット</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="39" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>11:00〜11:21</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+    <row r="14" ht="39" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>11:50〜12:11</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>同じ</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>購入者
 商品、窓辺</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>⑧ S4 なぜ選んだか
 1枚目 インタビューに戻る（同じ画角）→ 2枚目 空間の引き → 3枚目 窓辺の一枚。</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>9秒</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>3カット</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="39" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>11:21〜11:35</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
+    <row r="15" ht="39" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>12:11〜12:25</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>店舗の窓辺（S3と同じ画角）</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>購入者
 ―</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>⑧ S6 本音
 1枚目 表情のアップ → 2枚目 外の引きに人が入る → 3枚目 静かな一枚。</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>12秒</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>3カット</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="39" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>11:45〜12:20</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>店内のレジまわり → 店の前の街</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>くさがやさん、購入者
-商品、ノートPC</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>⑤ S6 購入・使う
-1枚目 会計の引き → 2枚目 手渡しと笑顔 → 3枚目 使っている手元。</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>7秒</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>同じ購入者に、会計から使う場面まで。購入者はここまで。
-3カット</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>12:20〜13:10</t>
+          <t>12:25〜13:15</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1571,7 +1573,7 @@
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>13:10〜13:25</t>
+          <t>13:15〜13:30</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1606,7 +1608,7 @@
     <row r="18" ht="39" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>13:25〜13:58</t>
+          <t>13:30〜14:03</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1641,7 +1643,7 @@
     <row r="19" ht="39" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>13:58〜14:20</t>
+          <t>14:03〜14:25</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1675,7 +1677,7 @@
     <row r="20" ht="39" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>14:20〜14:43</t>
+          <t>14:25〜14:47</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -1702,7 +1704,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>台を一度組んだら五シーン続けて。人が入る画はくさがやさんの肩から先だけ。
+          <t>くさがやさんの手。S4だけ四日目に工房で撮る。人が入る画は肩から先だけ。
 2カット</t>
         </is>
       </c>
@@ -1710,7 +1712,7 @@
     <row r="21" ht="39" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>14:43〜15:06</t>
+          <t>14:47〜15:09</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1744,7 +1746,7 @@
     <row r="22" ht="39" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>15:06〜15:34</t>
+          <t>15:09〜15:42</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -1778,7 +1780,7 @@
     <row r="23" ht="39" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>15:34〜15:57</t>
+          <t>15:42〜16:07</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1787,57 +1789,23 @@
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>くさがやさん（手だけ・白手袋）
-金具</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>③ S4 金具
-1枚目 金具を取り付ける（白手袋）→ 2枚目 手に取って確かめる（超マクロ）→ 3枚目 金具の寄り。</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>4秒</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>3カット</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="39" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>15:57〜16:25</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>同じ</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>佐藤さん（シルエット・1枚目だけ）
 完成品、工房の道具、ロゴ</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>③ S5 完成
 1枚目 黒の中に、作業する人のシルエット（佐藤さん・引き） → 2枚目 店の奥で持ち上げる（背景に道具）→ 3枚目 黒に戻して両手で持つ（上から一灯）→ 4枚目 作業台に立つ（引き）→ 5枚目 ロゴ。</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>5秒</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>4カット（1枚目は四日目に撮る）</t>
         </is>
@@ -2287,7 +2255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2636,66 +2604,101 @@
       </c>
     </row>
     <row r="16" ht="39" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>13:35〜14:05</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>工房の一角（③・黒スチレンボード）</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>佐藤さん黒スチレンボード、ライト一灯</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>③ 佐藤さんのシーン
-手元の寄りと、肩から先だけが光に入る一枚。顔は闇に置く。</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>30分</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>二日目と同じ光の向き・高さ・距離で組む。数字を控えてある。</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>13:35〜13:55</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>向島工房の一角（③の台を組み直す）</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>くさがやさん（手だけ・白手袋）
+金具</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>③ S4 金具
+1枚目 金具を取り付ける（白手袋）→ 2枚目 手に取って確かめる（超マクロ）→ 3枚目 金具の寄り。</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>4秒</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>二日目と同じ光の向き・高さ・距離・同じケルビンで組む。白手袋なので、手の違いが出ない。
+3カット</t>
         </is>
       </c>
     </row>
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
+          <t>13:55〜14:05</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>同じ台</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>佐藤さん黒スチレンボード、ライト一灯</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>③S5 1枚目
+黒の中に、作業する人のシルエット（引き）。顔も手も見えない。</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>10分</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>組み替えない。そのまま撮る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="39" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
           <t>14:20〜14:50</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>向島工房（窓を横に・他社の品が入らない一角）</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>佐藤さん
 椅子、レコーダー</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>⑥ インタビュー</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>三十分</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr"/>
+      <c r="F18" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>全八本 139カット ／ 撮影 五日 ／ 日付は10月中で未定</t>
+          <t>全八本 141カット ／ 撮影 五日 ／ 日付は10月中で未定</t>
         </is>
       </c>
     </row>
@@ -591,18 +591,18 @@
         <is>
           <t>⑧ 購入者インタビュー ── 店の前と店内、窓辺のインタビュー、外に出て使う場面、見送り
 ⑤ コーポレートムービー ── 購入・使う（会計・手渡し・使っている手元）
-② ASMRで製造の姿を撮る ── 下仕事とコバ塗り（店舗の作業台）　くさがやさんのシーン
-③ 暗めでエレガントにブランドを映す ── 五シーンすべて（店舗内の作業台）　くさがやさんのシーン</t>
+② ASMRで製造の姿を撮る ── くさがやさんの引き二枚と目元一枚（S4のぶんだけ）
+③ 暗めでエレガントにブランドを映す ── 五シーンすべて（店舗内の作業台）　くさがやさんがメイン</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>9:00〜16:07</t>
+          <t>9:00〜15:47</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>41カット</t>
+          <t>40カット</t>
         </is>
       </c>
     </row>
@@ -646,19 +646,19 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>② ASMRで製造の姿を撮る ── 革の棚・裁断・貼り合わせ・縫製・組み・完成　佐藤さんのシーン
+          <t>② ASMRで製造の姿を撮る ── 八シーンすべて　佐藤さんが一つの鞄を頭から作りきる
 ⑥ OEM工房案内 ── 佐藤さんのインタビュー
 ③ 暗めでエレガントにブランドを映す ── 佐藤さんのシーン（工房の一角・黒スチレンボード）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>9:30〜14:50</t>
+          <t>9:30〜15:30</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>24カット</t>
+          <t>27カット</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>① 服装ごとに画が変わる ── ロビーの四シーン（一色目〜四色目）
+          <t>① 服装ごとに画が変わる ── 六シーンすべて（外の歩道 → 横断歩道 → 渡った先の通り → 扉 → ロビー）
 ④ 鞄を持って街を歩く（海外ドラマ風） ── 柵（最初と最後）、置き画、けやき並木の歩道を歩く
 ⑤ コーポレートムービー ── 冒頭の俯瞰（表参道を高いところから）</t>
         </is>
@@ -1189,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>9:00〜16:07</t>
+          <t>9:00〜15:47</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>店の休みの日（月曜か火曜）に撮る。②の店舗ぶんは、裁断と貼り合わせを先に済ませたパーツを用意しておく。③は窓の光が入らない一角で、蛍光灯を全部消す。</t>
+          <t>店の休みの日（月曜か火曜）に撮る。②でこの日に撮るのは引きと目元だけなので、くさがやさんの手元には縫いかけのパーツが一つあればよい。仕上がっている必要はない。③は窓の光が入らない一角で、蛍光灯を全部消す。</t>
         </is>
       </c>
     </row>
@@ -1303,42 +1303,42 @@
     <row r="9" ht="39" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>9:00〜9:25</t>
+          <t>9:00〜9:30</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>店の前 → 入口 → 店の中</t>
+          <t>店の前 → 入口 → 店の中（開店準備）</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>購入者（外から中へ入る）
-店の外観、入口の扉、商品</t>
+          <t>購入者（顔まで入る）、くさがやさん（または内藤さん・渡辺さん）
+店の外観、入口の扉、開店準備の商品と棚、レジ</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
           <t>⑧ S1 外から中へ
-1枚目 外観のロー（見上げ）→ 2枚目 外から中へ入っていく（全景の引きから扉を抜けるまで切らずに追う）→ 3枚目 中に入って手元の寄り。</t>
+1枚目 外観のロー（見上げ）→ 2枚目 購入者が外から中へ入っていく（全景の引きから扉を抜けるまで切らずに追う）→ 3枚目 中に入って開店準備の手元の寄り → 4枚目 開店準備をしている引き → 5枚目 店に入って選んで買う（引き）。</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>5秒</t>
+          <t>6秒</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>つかみと見送りは同じ立ち位置。設営は一度。
-3カット</t>
+          <t>つかみと見送りは同じ立ち位置。設営は一度。開店準備の手元と引きは、購入者が入ってくる前にこの枠で撮る。
+4カット（5枚目は撮らない ── ⑤S6で撮ったカットを使う）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="39" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>9:25〜9:45</t>
+          <t>9:30〜9:55</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>購入者、くさがやさん（見送る役）
+          <t>購入者、くさがやさん（見送る役）　ともに顔まで入る
 ロゴ</t>
         </is>
       </c>
@@ -1372,7 +1372,7 @@
     <row r="11" ht="39" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>9:55〜10:20</t>
+          <t>10:05〜10:30</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>購入者
+          <t>購入者（顔まで入る）
 鞄、店の前の通り、空</t>
         </is>
       </c>
@@ -1407,7 +1407,7 @@
     <row r="12" ht="39" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>10:30〜11:05</t>
+          <t>10:40〜11:15</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>くさがやさん、購入者
+          <t>くさがやさん（または内藤さん・渡辺さん。⑧S1で開店準備をした人と同じ）、購入者
 商品、ノートPC</t>
         </is>
       </c>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>会計から使う場面まで。ここまでで、話す前にカメラに慣れてもらう。
+          <t>会計から使う場面まで。ここまでで、話す前にカメラに慣れてもらう。⑧S1の5枚目（店に入って選んで買う引き）も、ここで一本多めに撮っておく。応対するのは⑧S1で開店準備をしていた人。服は変えない。
 3カット</t>
         </is>
       </c>
@@ -1442,7 +1442,7 @@
     <row r="13" ht="39" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>11:15〜11:50</t>
+          <t>11:25〜12:00</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>購入者
+          <t>購入者（顔まで入る）
 商品、手前に置く植物</t>
         </is>
       </c>
@@ -1477,7 +1477,7 @@
     <row r="14" ht="39" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>11:50〜12:11</t>
+          <t>12:00〜12:21</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>購入者
+          <t>購入者（顔まで入る）
 商品、窓辺</t>
         </is>
       </c>
@@ -1511,7 +1511,7 @@
     <row r="15" ht="39" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>12:11〜12:25</t>
+          <t>12:21〜12:35</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1521,8 +1521,8 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>購入者
-―</t>
+          <t>購入者（顔まで入る）
+表情のアップ</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1545,7 +1545,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>12:25〜13:15</t>
+          <t>12:35〜13:25</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>13:15〜13:30</t>
+          <t>13:25〜13:40</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>6秒</t>
+          <t>5秒</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1606,113 +1606,111 @@
       </c>
     </row>
     <row r="18" ht="39" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>13:30〜14:03</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>店舗の作業台（下仕事）</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>くさがやさん（手だけ）
-刃、道具、革</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>② S5 縁を整える
-1枚目 刃で切り込み（超マクロ）→ 2枚目 縫い代を開く（斜め上から）→ 3枚目 指で縁を起こす（寄り）→ 4枚目 道具を当ててならす（横）。</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>6秒</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>くさがやさんの手。コバ塗りは切らずに六秒回す。
-4カット</t>
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>13:40〜14:05</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>店舗の作業台（②・くさがやさんの引きと目元）</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>くさがやさん縫いかけのパーツ、手縫いの道具</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>②S4 2枚目・3枚目・4枚目
+引き（手縫いをしている全身）／目元だけの寄り（手も品も入れない）／もう一段引く。</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>25分</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>手元の品が読める寄りは撮らない。四日目と同じ光の向き・高さ・距離、同じケルビンで組む。頭でグレーカードを一枚。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="39" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>14:03〜14:25</t>
+          <t>14:05〜14:27</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>店舗の作業台（コバ塗り・超マクロが組める台）</t>
+          <t>店舗内の作業台</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>くさがやさん（手だけ）
-コバ塗料、道具、断面</t>
+          <t>―
+鞄の一部（光の帯だけ）、黒スチレンボード</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>② S6 コバ塗り
-1枚目 超マクロ・三脚固定。</t>
+          <t>③ S1 超マクロ
+1枚目 光の帯が一本立つ → 2枚目 帯がゆっくり動く。</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>6秒</t>
+          <t>3秒</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>1カット</t>
+          <t>くさがやさんの手。始めと終わりはくさがやさん。S4だけ四日目に工房で撮る。人が入る画は肩から先だけ。
+2カット</t>
         </is>
       </c>
     </row>
     <row r="20" ht="39" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>14:25〜14:47</t>
+          <t>14:27〜14:49</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>店舗内の作業台</t>
+          <t>同じ</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>―
-鞄の一部（光の帯だけ）、黒スチレンボード</t>
+          <t>くさがやさん（手だけ・時計と指輪は外す）
+革 二枚、染料、道具</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>③ S1 超マクロ
-1枚目 光の帯が一本立つ → 2枚目 帯がゆっくり動く。</t>
+          <t>③ S2 貼り合わせ
+1枚目 革を置く → 2枚目 二枚を合わせる → 3枚目 押さえる。手だけ。三脚固定でカメラは動かさない。</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>3秒</t>
+          <t>4秒</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>くさがやさんの手。S4だけ四日目に工房で撮る。人が入る画は肩から先だけ。
-2カット</t>
+          <t>3カット</t>
         </is>
       </c>
     </row>
     <row r="21" ht="39" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>14:47〜15:09</t>
+          <t>14:49〜15:22</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1722,31 +1720,31 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>くさがやさん（手だけ・時計と指輪は外す）
-革 二枚、染料、道具</t>
+          <t>くさがやさん（手と肩）
+革</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>③ S2 貼り合わせ
-1枚目 革を置く → 2枚目 二枚を合わせる → 3枚目 押さえる。手だけ。三脚固定でカメラは動かさない。</t>
+          <t>③ S3 形をつくる
+1枚目 革を折り上げる → 2枚目 縁を押さえる（超マクロ）→ 3枚目 角が立ち上がる → 4枚目 肩から先だけが光に入る（くさがやさん）。</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>4秒</t>
+          <t>5秒</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>3カット</t>
+          <t>4カット</t>
         </is>
       </c>
     </row>
     <row r="22" ht="39" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>15:09〜15:42</t>
+          <t>15:22〜15:47</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -1755,57 +1753,23 @@
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>くさがやさん（手と肩）
-革</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>③ S3 形をつくる
-1枚目 革を折り上げる → 2枚目 縁を押さえる（超マクロ）→ 3枚目 角が立ち上がる → 4枚目 肩から先だけが光に入る（くさがやさん）。</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>5秒</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>4カット</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="39" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>15:42〜16:07</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>同じ</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>佐藤さん（シルエット・1枚目だけ）
 完成品、工房の道具、ロゴ</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>③ S5 完成
 1枚目 黒の中に、作業する人のシルエット（佐藤さん・引き） → 2枚目 店の奥で持ち上げる（背景に道具）→ 3枚目 黒に戻して両手で持つ（上から一灯）→ 4枚目 作業台に立つ（引き）→ 5枚目 ロゴ。</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>5秒</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>4カット（1枚目は四日目に撮る）</t>
         </is>
@@ -2255,7 +2219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2310,7 +2274,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>9:30〜14:50</t>
+          <t>9:30〜15:30</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2294,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>佐藤さんの休日に合わせる。工房が止まっているので、出入りの音が入らない。②の録音にはこの日でないといけない。機械は佐藤さんに動かしてもらう。</t>
+          <t>佐藤さんの休日に合わせる。工房が止まっているので、出入りの音が入らない。②の録音にはこの日でないといけない。機械は佐藤さんに動かしてもらう。佐藤さんは店舗には行かない。②③で佐藤さんが映るカットは、すべてこの日にまとめる。</t>
         </is>
       </c>
     </row>
@@ -2484,14 +2448,14 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん（手と上半身）
-ミシン、糸、革</t>
+          <t>佐藤さん（手と上半身）、くさがやさん（引きと目元だけ）
+ミシン、糸、革、手縫いの道具</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
           <t>② S4 縫う
-1枚目 針の超マクロ → 2枚目 工房の引き（人が入る）→ 3枚目 手縫いの寄り → 4枚目もう一段引く。</t>
+1枚目 針の超マクロ（工房・佐藤さん）→ 2枚目 引き・手縫い（店舗・くさがやさん）→ 3枚目 目元だけの寄り（店舗・くさがやさん）→ 4枚目 もう一段引く（店舗）→ 5枚目 手縫いの寄り（工房・佐藤さん）。</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -2502,7 +2466,7 @@
       <c r="F12" s="5" t="inlineStr">
         <is>
           <t>寄りと引きを交互に。
-4カット</t>
+2カット（2枚目・3枚目・4枚目は二日目に撮る）</t>
         </is>
       </c>
     </row>
@@ -2537,168 +2501,237 @@
     <row r="14" ht="39" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>12:35〜13:06</t>
+          <t>12:35〜13:08</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>作業台（引きが撮れる位置まで下がれるところ）</t>
+          <t>工房の作業台（下仕事・超マクロが組める台）</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>佐藤さん（手だけ）
+刃、道具、革</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>② S5 縁を整える
+1枚目 刃で切り込み（超マクロ）→ 2枚目 縫い代を開く（斜め上から）→ 3枚目 指で縁を起こす（寄り）→ 4枚目 道具を当ててならす（横）。</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>6秒</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S4までと同じ鞄をそのまま続けて撮る。コバ塗りは切らずに六秒回す。
+4カット</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="39" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>13:08〜13:30</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>同じ台（コバ塗り）</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>佐藤さん（手だけ）
+コバ塗料、道具、断面</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>② S6 コバ塗り
+1枚目 超マクロ・三脚固定。</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>6秒</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>1カット</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="39" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>13:30〜14:01</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>同じ台（引きが撮れる位置まで下がれるところ）</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>佐藤さん（手と上半身）
 木槌、道具、立ち上がった鞄</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>② S7 仕上げる
 1枚目 作業台の引き → 2枚目 立ち上がった形を持つ（胸の高さ）→ 3枚目 木槌で底を打つ（横）→ 4枚目 コバを整える（寄り）→ 5枚目 縁に印（寄り）。</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>5秒</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>二シーンとも同じ画角。続けて撮る。
 5カット</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="39" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>13:06〜13:25</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>工房の作業台（S7と同じ場所・同じ画角）</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
+    <row r="17" ht="39" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>14:01〜14:20</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>同じ台（S7と同じ画角）</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>佐藤さん（手だけ）
 完成した鞄、ロゴ</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>② S8 完成
 1枚目 最後の一手（寄り）→ 2枚目 持ち上げる（横）→ 3枚目 白バックのロゴ。</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>4秒</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>3カット</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="39" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>13:35〜13:55</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+    <row r="18" ht="39" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>14:30〜14:50</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>向島工房の一角（③の台を組み直す）</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>くさがやさん（手だけ・白手袋）
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>佐藤さん（手だけ・白手袋）
 金具</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>③ S4 金具
 1枚目 金具を取り付ける（白手袋）→ 2枚目 手に取って確かめる（超マクロ）→ 3枚目 金具の寄り。</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>4秒</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>二日目と同じ光の向き・高さ・距離・同じケルビンで組む。白手袋なので、手の違いが出ない。
 3カット</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="39" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>13:55〜14:05</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
+    <row r="19" ht="39" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>14:50〜15:00</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>同じ台</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>佐藤さん黒スチレンボード、ライト一灯</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>③S5 1枚目
 黒の中に、作業する人のシルエット（引き）。顔も手も見えない。</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>10分</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>組み替えない。そのまま撮る。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="39" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>14:20〜14:50</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
+    <row r="20" ht="39" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>15:00〜15:30</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>向島工房（窓を横に・他社の品が入らない一角）</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>佐藤さん
 椅子、レコーダー</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>⑥ インタビュー</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>三十分</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr"/>
+      <c r="F20" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2825,241 +2858,242 @@
     <row r="9" ht="39" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>9:00〜9:41</t>
+          <t>9:00〜9:24</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>東京国際フォーラム ガラス棟ロビーの通路</t>
+          <t>東京国際フォーラム 地上広場のけやきぎわの歩道</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>モデル
+一色目の衣装・鞄</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>① S1 一色目
+1枚目 全身の引き・正面（けやきとガラス棟が背景に入る）→ 2枚目 同じ位置から腰より上。</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>5秒</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>一色目はけやきとガラス棟を背景に。二色目は横断歩道を渡りきるところで、目の前を車が通り過ぎた一コマでつなぐ。
+2カット</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="39" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>9:24〜9:54</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>フォーラム前の横断歩道（渡りきるところ）</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>モデル
+二色目の衣装・鞄</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>① S2 二色目
+1枚目 引き → 2枚目 腰より上。</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>5秒</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>2カット</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="39" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>9:54〜10:12</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>渡った先の通り（丸の内仲通り側のけやき並木）</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>モデル
+三色目の衣装・鞄</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>① S3 三色目
+1枚目 引き → 2枚目 腰より上。</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>5秒</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>三色目はけやきの後ろを通った一瞬、四色目は扉をまたいだ一コマでつなぐ。S3とS4のあいだで来た道を戻るが、画角が違うので見ている人には分からない。扉の画に横断歩道を入れない。
+2カット</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="39" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>10:12〜10:31</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>ガラス棟の扉（またいで中へ入る）</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>モデル
+四色目の衣装・鞄</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>① S4 四色目
+1枚目 引き → 2枚目 腰より上（鞄を掛け直して笑う）。</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>5秒</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>2カット</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="39" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>10:31〜11:12</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>ガラス棟ロビーの通路</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>モデル、通行人（すれ違う役）
 四色ぶんの衣装・鞄</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>① S5 巻き戻る
 1枚目 ロビーの通路を歩く（横移動で追う・三脚キャスター）→ 2枚目 腰より上。</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>7秒</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>廊下を歩く。四色を並べるポーズもここで。
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>通路を歩いて巻き戻る。四色を並べるポーズもここで。
 2カット</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="39" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>9:41〜10:10</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
+    <row r="14" ht="39" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>11:12〜11:41</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>ロビーのベンチ（四色を並べる位置）</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>モデル 四色ぶん
 鞄 四種類、ロゴ</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>① S6 四種類並べて終わる
 1枚目 鞄の寄り → 2枚目 四色が並ぶ（ロビーのベンチ）→ 3枚目 白バックのロゴ。三つとも三脚固定。</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>8秒</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>3カット</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>10:10〜11:10</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>11:41〜12:41</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>移動（有楽町 → 表参道）</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>1時間0分</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr"/>
-    </row>
-    <row r="12" ht="39" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>11:10〜11:34</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>表参道 けやき並木の歩道（並木通りが入る位置）</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>モデル
-一色目の衣装・鞄</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>① S1 一色目
-1枚目 全身の引き・正面（並木通りが入る）→ 2枚目 同じ位置から腰より上。</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>5秒</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>進む側の四シーン。切り替わりは 車・木・ドア。
-2カット</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="39" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>11:34〜11:58</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>車道ぎわの歩道（車が通り過ぎる位置）</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>モデル
-二色目の衣装・鞄</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>① S2 二色目
-1枚目 引き → 2枚目 腰より上。</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>5秒</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>2カット</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="39" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>11:58〜12:16</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>けやき並木の木の前</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>モデル
-三色目の衣装・鞄</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>① S3 三色目
-1枚目 引き → 2枚目 腰より上。</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>5秒</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>2カット</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="39" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>12:16〜12:35</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>店やビルのドアの前</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>モデル
-四色目の衣装・鞄</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>① S4 四色目
-1枚目 引き → 2枚目 腰より上（鞄を掛け直して笑う）。</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>5秒</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>2カット</t>
-        </is>
-      </c>
+      <c r="F15" s="10" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>12:35〜13:35</t>
+          <t>12:41〜13:35</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -3079,7 +3113,7 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>1時間0分</t>
+          <t>54分</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
@@ -3483,7 +3517,7 @@
         <is>
           <t>顔出しの範囲を、撮る前に本人へ確認する。
 名前は出さず「購入者Aさん」とだけ出す。
-拘束は 9:00〜11:45。日は購入者が決まってから決める。</t>
+拘束は 9:00〜12:35。日は購入者が決まってから決める。</t>
         </is>
       </c>
     </row>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>9:00〜13:40</t>
+          <t>9:00〜14:10</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>9:00〜13:40</t>
+          <t>9:00〜14:10</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
     <row r="19" ht="39" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>13:10〜13:40</t>
+          <t>13:10〜14:10</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>人が映らないカット。
+          <t>人が映らないカット。一時間取る。棚・照明・ショーウィンドウを、インタビューで出た言葉に合わせて撮り足せるようにしておく。
 2カット</t>
         </is>
       </c>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -592,17 +592,17 @@
           <t>⑧ 購入者インタビュー ── 店の前と店内、窓辺のインタビュー、外に出て使う場面、見送り
 ⑤ コーポレートムービー ── 購入・使う（会計・手渡し・使っている手元）
 ② ASMRで製造の姿を撮る ── くさがやさんの引き二枚と目元一枚（S4のぶんだけ）
-③ 暗めでエレガントにブランドを映す ── 五シーンすべて（店舗内の作業台）　くさがやさんがメイン</t>
+③ 暗めでエレガントにブランドを映す ── 五シーンすべて（店舗内の作業台）　くさがやさんが通しで作る</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>9:00〜15:47</t>
+          <t>9:00〜16:07</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>40カット</t>
+          <t>42カット</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
         <is>
           <t>② ASMRで製造の姿を撮る ── 八シーンすべて　佐藤さんが一つの鞄を頭から作りきる
 ⑥ OEM工房案内 ── 佐藤さんのインタビュー
-③ 暗めでエレガントにブランドを映す ── 佐藤さんのシーン（工房の一角・黒スチレンボード）</t>
+③ 暗めでエレガントにブランドを映す ── 佐藤さんの二枚（目元と引き・工房の一角）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>9:30〜15:30</t>
+          <t>9:30〜15:35</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>27カット</t>
+          <t>25カット</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>9:00〜15:47</t>
+          <t>9:00〜16:07</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>くさがやさんの手。始めと終わりはくさがやさん。S4だけ四日目に工房で撮る。人が入る画は肩から先だけ。
+          <t>五シーンとも、くさがやさんが頭から通して作る。工程は分けない。佐藤さんの二枚（S3 4枚目の目元・S5 1枚目の引き）だけ四日目に工房で撮る。
 2カット</t>
         </is>
       </c>
@@ -1720,14 +1720,14 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>くさがやさん（手と肩）
+          <t>くさがやさん（手）。4枚目だけ佐藤さん（目元）
 革</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
           <t>③ S3 形をつくる
-1枚目 革を折り上げる → 2枚目 縁を押さえる（超マクロ）→ 3枚目 角が立ち上がる → 4枚目 肩から先だけが光に入る（くさがやさん）。</t>
+1枚目 革を折り上げる → 2枚目 縁を押さえる（超マクロ）→ 3枚目 角が立ち上がる → 4枚目 目元だけが光に入る（佐藤さん・寄り）。</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1737,14 +1737,14 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>4カット</t>
+          <t>3カット（4枚目は四日目に撮る）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="39" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>15:22〜15:47</t>
+          <t>15:22〜15:42</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -1753,23 +1753,57 @@
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>くさがやさん（手だけ・白手袋）
+金具</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>③ S4 金具
+1枚目 金具を取り付ける（白手袋）→ 2枚目 手に取って確かめる（超マクロ）→ 3枚目 金具の寄り。</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>4秒</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>3カット</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="39" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>15:42〜16:07</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>同じ</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>佐藤さん（シルエット・1枚目だけ）
 完成品、工房の道具、ロゴ</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>③ S5 完成
 1枚目 黒の中に、作業する人のシルエット（佐藤さん・引き） → 2枚目 店の奥で持ち上げる（背景に道具）→ 3枚目 黒に戻して両手で持つ（上から一灯）→ 4枚目 作業台に立つ（引き）→ 5枚目 ロゴ。</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>5秒</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>4カット（1枚目は四日目に撮る）</t>
         </is>
@@ -2219,7 +2253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2274,7 +2308,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>9:30〜15:30</t>
+          <t>9:30〜15:35</t>
         </is>
       </c>
     </row>
@@ -2636,102 +2670,69 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="39" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>14:30〜14:50</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>向島工房の一角（③の台を組み直す）</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>佐藤さん（手だけ・白手袋）
-金具</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>③ S4 金具
-1枚目 金具を取り付ける（白手袋）→ 2枚目 手に取って確かめる（超マクロ）→ 3枚目 金具の寄り。</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>4秒</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>二日目と同じ光の向き・高さ・距離・同じケルビンで組む。白手袋なので、手の違いが出ない。
-3カット</t>
+    <row r="18" ht="65" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>14:30〜14:55</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>工房の一角（③・黒スチレンボード）</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>佐藤さん黒スチレンボード、ライト一灯</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>③S3 4枚目
+闇の中に、目元だけが光に入る（寄り）。
+③S5 1枚目
+黒の中に、作業する人のシルエット（引き）。顔も手も見えない。</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>25分</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>二日目と同じ光の向き・高さ・距離・同じケルビンで組む。手も品も画に入れない。だから工程が切れない。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="39" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>14:50〜15:00</t>
+          <t>15:05〜15:35</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>同じ台</t>
+          <t>向島工房（窓を横に・他社の品が入らない一角）</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>佐藤さん黒スチレンボード、ライト一灯</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>③S5 1枚目
-黒の中に、作業する人のシルエット（引き）。顔も手も見えない。</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>10分</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>組み替えない。そのまま撮る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="39" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>15:00〜15:30</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>向島工房（窓を横に・他社の品が入らない一角）</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>佐藤さん
 椅子、レコーダー</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>⑥ インタビュー</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>三十分</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr"/>
+      <c r="F19" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -1314,13 +1314,13 @@
       <c r="C9" s="5" t="inlineStr">
         <is>
           <t>購入者（顔まで入る）、くさがやさん（または内藤さん・渡辺さん）
-店の外観、入口の扉、開店準備の商品と棚、レジ</t>
+店の外観、入口の扉、商品と棚、レジ</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
           <t>⑧ S1 外から中へ
-1枚目 外観のロー（見上げ）→ 2枚目 購入者が外から中へ入っていく（全景の引きから扉を抜けるまで切らずに追う）→ 3枚目 中に入って開店準備の手元の寄り → 4枚目 開店準備をしている引き → 5枚目 店に入って選んで買う（引き）。</t>
+1枚目 外観のロー（見上げ）→ 2枚目 購入者が外から中へ入っていく（全景の引きから扉を抜けるまで切らずに追う）→ 3枚目 中に入って商品と手元の寄り → 4枚目 開店準備をしている引き → 5枚目 店に入って選んで買う（引き）。</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>つかみと見送りは同じ立ち位置。設営は一度。開店準備の手元と引きは、購入者が入ってくる前にこの枠で撮る。
+          <t>つかみと見送りは同じ立ち位置。設営は一度。商品と手元の寄り、開店準備の引きは、購入者が入ってくる前にこの枠で撮る。
 4カット（5枚目は撮らない ── ⑤S6で撮ったカットを使う）</t>
         </is>
       </c>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -1313,14 +1313,14 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>購入者（顔まで入る）、くさがやさん（または内藤さん・渡辺さん）
+          <t>購入者（顔まで入る）、店の人（3枚目の手元）
 店の外観、入口の扉、商品と棚、レジ</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
           <t>⑧ S1 外から中へ
-1枚目 外観のロー（見上げ）→ 2枚目 購入者が外から中へ入っていく（全景の引きから扉を抜けるまで切らずに追う）→ 3枚目 中に入って商品と手元の寄り → 4枚目 開店準備をしている引き → 5枚目 店に入って選んで買う（引き）。</t>
+1枚目 外観のロー（見上げ）→ 2枚目 購入者が外から中へ入っていく（全景の引きから扉を抜けるまで切らずに追う）→ 3枚目 中に入って商品と手元の寄り → 4枚目 店に入って選んで買う（引き）。</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1330,8 +1330,8 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>つかみと見送りは同じ立ち位置。設営は一度。商品と手元の寄り、開店準備の引きは、購入者が入ってくる前にこの枠で撮る。
-4カット（5枚目は撮らない ── ⑤S6で撮ったカットを使う）</t>
+          <t>つかみと見送りは同じ立ち位置。設営は一度。商品と手元の寄りは、購入者が入ってくる前にこの枠で撮る。
+4カット</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>くさがやさん（または内藤さん・渡辺さん。⑧S1で開店準備をした人と同じ）、購入者
+          <t>くさがやさん（または内藤さん・渡辺さん。⑧S1の3枚目で手元が映る人と同じ）、購入者
 商品、ノートPC</t>
         </is>
       </c>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>会計から使う場面まで。ここまでで、話す前にカメラに慣れてもらう。⑧S1の5枚目（店に入って選んで買う引き）も、ここで一本多めに撮っておく。応対するのは⑧S1で開店準備をしていた人。服は変えない。
+          <t>会計から使う場面まで。ここまでで、話す前にカメラに慣れてもらう。⑧S1の4枚目（店に入って選んで買う引き）も、ここで続けて撮る。応対するのは⑧S1の3枚目で手元が映る人。服は変えない。
 3カット</t>
         </is>
       </c>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>―
+          <t>工房のチーム（棚のそばに入ってよい）
 革のロールが並ぶ棚</t>
         </is>
       </c>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん（手だけ）
+          <t>佐藤さんと工房のチーム
 抜き型、革、裁断機</t>
         </is>
       </c>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん（手だけ）
+          <t>佐藤さんと工房のチーム
 革 二枚、型</t>
         </is>
       </c>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん（手と上半身）、くさがやさん（引きと目元だけ）
+          <t>佐藤さんと工房のチーム、くさがやさん（引きと目元だけ）
 ミシン、糸、革、手縫いの道具</t>
         </is>
       </c>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん（手だけ）
+          <t>佐藤さんと工房のチーム
 刃、道具、革</t>
         </is>
       </c>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん（手だけ）
+          <t>佐藤さんと工房のチーム
 コバ塗料、道具、断面</t>
         </is>
       </c>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん（手と上半身）
+          <t>佐藤さんと工房のチーム
 木槌、道具、立ち上がった鞄</t>
         </is>
       </c>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん（手だけ）
+          <t>佐藤さんと工房のチーム
 完成した鞄、ロゴ</t>
         </is>
       </c>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>全八本 141カット ／ 撮影 五日 ／ 日付は10月中で未定</t>
+          <t>全八本 139カット ／ 撮影 五日 ／ 日付は10月中で未定</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>25カット</t>
+          <t>24カット</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>26カット</t>
+          <t>25カット</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>東京国際フォーラム 地上広場のけやきぎわの歩道</t>
+          <t>丸の内仲通りのけやき並木（北から南へ歩く）</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2876,7 +2876,7 @@
       <c r="D9" s="5" t="inlineStr">
         <is>
           <t>① S1 一色目
-1枚目 全身の引き・正面（けやきとガラス棟が背景に入る）→ 2枚目 同じ位置から腰より上。</t>
+1枚目 全身の引き・正面（仲通りのけやき並木が奥まで抜ける）→ 2枚目 同じ位置から腰より上。</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>フォーラム前の横断歩道（渡りきるところ）</t>
+          <t>東京国際フォーラム東交差点の横断歩道（渡りきるところ）</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>渡った先の通り（丸の内仲通り側のけやき並木）</t>
+          <t>渡った先 ── フォーラム地上広場のけやきぎわ</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3315,7 +3315,7 @@
       <c r="D22" s="5" t="inlineStr">
         <is>
           <t>⑤ S1 空から入る
-1枚目 高いところから並木通りを見下ろす → 2枚目 寄っていく → 3枚目 永尾社長のバストショット。</t>
+1枚目 高いところから並木通りを見下ろす。一枚だけ、切らずに六秒。</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2カット（3枚目は一日目に撮る）</t>
+          <t>1カット</t>
         </is>
       </c>
     </row>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>9:00〜17:05</t>
+          <t>9:00〜16:37</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>9:00〜17:05</t>
+          <t>9:00〜16:37</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>一色目はけやきとガラス棟を背景に。二色目は横断歩道を渡りきるところで、目の前を車が通り過ぎた一コマでつなぐ。
+          <t>一色目は仲通りの並木が奥まで抜ける位置。二色目は横断歩道を渡りきるところで、目の前を車が通り過ぎた一コマでつなぐ。信号待ちが入るので三十分取る。
 2カット</t>
         </is>
       </c>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>三色目はけやきの後ろを通った一瞬、四色目は扉をまたいだ一コマでつなぐ。S3とS4のあいだで来た道を戻るが、画角が違うので見ている人には分からない。扉の画に横断歩道を入れない。
+          <t>三色目はけやきの後ろを通った一瞬、四色目は扉をまたいだ一コマでつなぐ。仲通りから扉まで、歩く向きを一度も変えない。
 2カット</t>
         </is>
       </c>
@@ -3195,110 +3195,110 @@
     <row r="19" ht="39" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>14:35〜15:03</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>ベンチか石段（真俯瞰が組めるところ）</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>モデル
+鞄、中に入れる持ち物</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>④ S2 中を見せる
+1枚目 口を開ける（真俯瞰）→ 2枚目 中身を整える手（真俯瞰の寄り）→ 3枚目 横にスライドして次へつなぐ。</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>7秒</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>モデルの手が真俯瞰で映る。鞄に入れる持ち物を先に並べておく。
+3カット</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="39" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>15:10〜15:35</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>けやき並木の裏の路地（人がほとんど通らない側）</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>モデル（後ろ姿）
 鞄</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>④ S3 街を歩く
 1枚目 並木の歩道を歩く（引き・固定）→ 2枚目 肩の鞄に寄る。</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>7秒</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>人の少ない裏側で。
 2カット</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="39" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="21" ht="39" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>15:35〜16:05</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>けやき並木の歩道（出演者はここまで）</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>モデル鞄</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>⑤ 使用シーンの追加素材
 街で鞄を持って歩く・手に取る・肩に掛け直す。</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>30分</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>切らずに長めに三本。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="39" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>16:15〜16:43</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>ベンチか石段（真俯瞰が組めるところ）</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>手だけ
-鞄、中に入れる持ち物</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>④ S2 中を見せる
-1枚目 口を開ける（真俯瞰）→ 2枚目 中身を整える手（真俯瞰の寄り）→ 3枚目 横にスライドして次へつなぐ。</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>7秒</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>人が映らないカット。まとめて撮る。
-3カット</t>
         </is>
       </c>
     </row>
     <row r="22" ht="39" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>16:43〜17:05</t>
+          <t>16:15〜16:37</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -3325,7 +3325,8 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>1カット</t>
+          <t>人が映らないカット。モデルが帰ったあとでよい。
+1カット</t>
         </is>
       </c>
     </row>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -923,7 +923,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>手だけ
+          <t>永尾社長ともう一人
 図面、型紙</t>
         </is>
       </c>
@@ -957,7 +957,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>出演者（手と肩だけ）
+          <t>出演者
 鞄、机</t>
         </is>
       </c>
@@ -992,7 +992,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>出演者（手だけ）
+          <t>出演者
 A4書類、13インチPC</t>
         </is>
       </c>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>出演者（手だけ）
+          <t>出演者
 手帳、鍵、サングラス、ペン、傘、水筒</t>
         </is>
       </c>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>出演者（手と肩だけ）
+          <t>出演者
 鞄</t>
         </is>
       </c>
@@ -1686,14 +1686,14 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>くさがやさん（手だけ・時計と指輪は外す）
+          <t>くさがやさん（時計と指輪は外す）
 革 二枚、染料、道具</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
           <t>③ S2 貼り合わせ
-1枚目 革を置く → 2枚目 二枚を合わせる → 3枚目 押さえる。手だけ。三脚固定でカメラは動かさない。</t>
+1枚目 革を置く → 2枚目 二枚を合わせる → 3枚目 押さえる。三脚固定でカメラは動かさない。</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>くさがやさん（手だけ・白手袋）
+          <t>くさがやさん（白手袋）
 金具</t>
         </is>
       </c>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>手だけ
+          <t>職人
 革の棚、金型、型紙</t>
         </is>
       </c>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>手だけ
+          <t>職人
 裁断機、革包丁、裁ち上がったパーツ</t>
         </is>
       </c>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>映らない（手と肩だけ）</t>
+          <t>映らない</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>永尾社長ともう一人（覗き込む役）
+          <t>永尾社長、くさがやさん
 色見本、革、店舗の机</t>
         </is>
       </c>
@@ -923,7 +923,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>永尾社長ともう一人
+          <t>永尾社長、くさがやさん
 図面、型紙</t>
         </is>
       </c>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>購入者（顔まで入る）、店の人（3枚目の手元）
+          <t>購入者、店の人
 店の外観、入口の扉、商品と棚、レジ</t>
         </is>
       </c>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>購入者、くさがやさん（見送る役）　ともに顔まで入る
+          <t>購入者、くさがやさん
 ロゴ</t>
         </is>
       </c>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>購入者（顔まで入る）
+          <t>購入者
 鞄、店の前の通り、空</t>
         </is>
       </c>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>くさがやさん（または内藤さん・渡辺さん。⑧S1の3枚目で手元が映る人と同じ）、購入者
+          <t>くさがやさん、購入者
 商品、ノートPC</t>
         </is>
       </c>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>購入者（顔まで入る）
+          <t>購入者
 商品、手前に置く植物</t>
         </is>
       </c>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>購入者（顔まで入る）
+          <t>購入者
 商品、窓辺</t>
         </is>
       </c>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>購入者（顔まで入る）
+          <t>購入者
 表情のアップ</t>
         </is>
       </c>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>くさがやさん（時計と指輪は外す）
+          <t>くさがやさん
 革 二枚、染料、道具</t>
         </is>
       </c>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>くさがやさん（手）。4枚目だけ佐藤さん（目元）
+          <t>くさがやさん、佐藤さん
 革</t>
         </is>
       </c>
@@ -1754,8 +1754,8 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>くさがやさん（白手袋）
-金具</t>
+          <t>くさがやさん
+金具、白手袋</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん（シルエット・1枚目だけ）
+          <t>くさがやさん、佐藤さん
 完成品、工房の道具、ロゴ</t>
         </is>
       </c>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>作業する人（顔は出さない）
+          <t>工房のチーム
 工房の入口、通路、機械</t>
         </is>
       </c>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん、作業する人
+          <t>佐藤さん、工房のチーム
 材料の壁、機械</t>
         </is>
       </c>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>職人（手と目）
+          <t>職人
 へら、スプレー、コバ塗料</t>
         </is>
       </c>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>職人（両手）
+          <t>職人
 ミシン、糸、部品</t>
         </is>
       </c>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>職人（手と横顔）
+          <t>職人
 上がった品</t>
         </is>
       </c>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>工房のチーム（棚のそばに入ってよい）
+          <t>工房のチーム
 革のロールが並ぶ棚</t>
         </is>
       </c>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>佐藤さんと工房のチーム
+          <t>佐藤さん、工房のチーム
 抜き型、革、裁断機</t>
         </is>
       </c>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>佐藤さんと工房のチーム
+          <t>佐藤さん、工房のチーム
 革 二枚、型</t>
         </is>
       </c>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>佐藤さんと工房のチーム、くさがやさん（引きと目元だけ）
+          <t>佐藤さん、工房のチーム、くさがやさん
 ミシン、糸、革、手縫いの道具</t>
         </is>
       </c>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>佐藤さんと工房のチーム
+          <t>佐藤さん、工房のチーム
 刃、道具、革</t>
         </is>
       </c>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>佐藤さんと工房のチーム
+          <t>佐藤さん、工房のチーム
 コバ塗料、道具、断面</t>
         </is>
       </c>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>佐藤さんと工房のチーム
+          <t>佐藤さん、工房のチーム
 木槌、道具、立ち上がった鞄</t>
         </is>
       </c>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>佐藤さんと工房のチーム
+          <t>佐藤さん、工房のチーム
 完成した鞄、ロゴ</t>
         </is>
       </c>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>モデル、通行人（すれ違う役）
+          <t>モデル、通行人
 四色ぶんの衣装・鞄</t>
         </is>
       </c>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>モデル 四色ぶん
+          <t>モデル
 鞄 四種類、ロゴ</t>
         </is>
       </c>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>モデル（後ろ姿）
+          <t>モデル
 鞄</t>
         </is>
       </c>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>9:00〜14:10</t>
+          <t>9:00〜13:40</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>9:00〜14:10</t>
+          <t>9:00〜13:40</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
     <row r="19" ht="39" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>13:10〜14:10</t>
+          <t>13:10〜13:40</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>人が映らないカット。一時間取る。棚・照明・ショーウィンドウを、インタビューで出た言葉に合わせて撮り足せるようにしておく。
+          <t>人が映らないカット。棚・照明・ショーウィンドウは、インタビューで出た言葉に合うものだけ選んで撮る。
 2カット</t>
         </is>
       </c>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -1469,7 +1469,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>ここからインタビュー。三シーン続けて。カメラは動かさない。購入者はここまで。
+          <t>ここからインタビュー。三シーン続けて。カメラは動かさない。
 3カット</t>
         </is>
       </c>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>全八本 139カット ／ 撮影 五日 ／ 日付は10月中で未定</t>
+          <t>全八本 135カット ／ 撮影 五日 ／ 日付は10月中で未定</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>42カット</t>
+          <t>38カット</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       <c r="D14" s="5" t="inlineStr">
         <is>
           <t>⑧ S4 なぜ選んだか
-1枚目 インタビューに戻る（同じ画角）→ 2枚目 空間の引き → 3枚目 窓辺の一枚。</t>
+1枚目 インタビューに戻る（同じ画角）。</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>3カット</t>
+          <t>1カット</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       <c r="D15" s="5" t="inlineStr">
         <is>
           <t>⑧ S6 本音
-1枚目 表情のアップ → 2枚目 外の引きに人が入る → 3枚目 静かな一枚。</t>
+1枚目 表情のアップ。</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>3カット</t>
+          <t>1カット</t>
         </is>
       </c>
     </row>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -1634,7 +1634,7 @@
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>手元の品が読める寄りは撮らない。四日目と同じ光の向き・高さ・距離、同じケルビンで組む。頭でグレーカードを一枚。</t>
+          <t>手元の品が読める寄りは撮らない。四日目と同じ光の向き・高さ・距離、同じケルビンで組む。</t>
         </is>
       </c>
     </row>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>⑥ OEM工房案内 ── 工房の全体と機械、革と金型、裁断、下仕事、縫製、検品、梱包</t>
+          <t>⑥ OEM工房案内 ── 工房の全体と機械、革と金型、裁断、下仕事、縫製、検品、梱包　── 日が分かれることがある</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>平日に撮る。機械が動いていて、人がいる時間。引きの画に人が入るので、⑥はこの日でないと成立しない。</t>
+          <t>平日に撮る。機械が動いていて、人がいる時間。画に入れられるのは、BROOKLYN MUSEUMの品を作っているところだけ。他社の品が流れている工程はその日に撮れないので、⑥は一日で撮り切れず、日が分かれることがある。工房に当日どの品を流すかを先に聞き、撮れる工程から順に回す。残った工程は別の平日に撮り足す。</t>
         </is>
       </c>
     </row>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -2001,7 +2001,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="39" customHeight="1">
+    <row r="11" ht="52" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>10:10〜10:45</t>
@@ -2032,6 +2032,7 @@
       <c r="F11" s="5" t="inlineStr">
         <is>
           <t>棚の奥行きが出る位置から。
+おまけ ── 革を作っているカワゼンさん・ミヤツグさんにも撮影をお願いしたい。別の日に撮る。日程は未定。
 3カット</t>
         </is>
       </c>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -2032,7 +2032,7 @@
       <c r="F11" s="5" t="inlineStr">
         <is>
           <t>棚の奥行きが出る位置から。
-おまけ ── 革を作っているカワゼンさん・ミヤツグさんにも撮影をお願いしたい。別の日に撮る。日程は未定。
+革を作っているカワゼンさん・ミヤツグさんにも撮影をお願いしたい。別の日に撮る。日程は未定。
 3カット</t>
         </is>
       </c>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -2001,7 +2001,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="52" customHeight="1">
+    <row r="11" ht="39" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>10:10〜10:45</t>
@@ -2031,8 +2031,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>棚の奥行きが出る位置から。
-革を作っているカワゼンさん・ミヤツグさんにも撮影をお願いしたい。別の日に撮る。日程は未定。
+          <t>棚の奥行きが出る位置から。革を作っているカワゼンさん・ミヤツグさんにも撮影をお願いしたい。別の日に撮る。日程は未定。
 3カット</t>
         </is>
       </c>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>職人
+          <t>パート
 上がった品</t>
         </is>
       </c>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん、梱包場の人
+          <t>パート、佐藤さん
 不織布、箱、テープ</t>
         </is>
       </c>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -1979,7 +1979,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん、工房のチーム
+          <t>工房のチーム
 材料の壁、機械</t>
         </is>
       </c>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>パート、佐藤さん
+          <t>パート
 不織布、箱、テープ</t>
         </is>
       </c>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>四日目　── 10月中（日にちは未定・佐藤さんの休日）</t>
+          <t>四日目　── 10月中（日にちは未定・休日）</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>佐藤さんの休日に合わせる。工房が止まっているので、出入りの音が入らない。②の録音にはこの日でないといけない。機械は佐藤さんに動かしてもらう。佐藤さんは店舗には行かない。②③で佐藤さんが映るカットは、すべてこの日にまとめる。</t>
+          <t>工房の休日に撮る。工房が止まっているので、出入りの音が入らない。②の録音にはこの日でないといけない。機械は佐藤さんに動かしてもらう。佐藤さんは店舗には行かない。②③で佐藤さんが映るカットは、すべてこの日にまとめる。</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>工房のチーム
+          <t>佐藤さん
 革のロールが並ぶ棚</t>
         </is>
       </c>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん、工房のチーム
+          <t>佐藤さん
 抜き型、革、裁断機</t>
         </is>
       </c>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん、工房のチーム
+          <t>佐藤さん
 革 二枚、型</t>
         </is>
       </c>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん、工房のチーム、くさがやさん
+          <t>佐藤さん
 ミシン、糸、革、手縫いの道具</t>
         </is>
       </c>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん、工房のチーム
+          <t>佐藤さん
 刃、道具、革</t>
         </is>
       </c>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん、工房のチーム
+          <t>佐藤さん
 コバ塗料、道具、断面</t>
         </is>
       </c>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん、工房のチーム
+          <t>佐藤さん
 木槌、道具、立ち上がった鞄</t>
         </is>
       </c>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>佐藤さん、工房のチーム
+          <t>佐藤さん
 完成した鞄、ロゴ</t>
         </is>
       </c>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>モデル
+          <t>モデル1
 一色目の衣装・鞄</t>
         </is>
       </c>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>モデル
+          <t>モデル1
 二色目の衣装・鞄</t>
         </is>
       </c>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>モデル
+          <t>モデル1
 三色目の衣装・鞄</t>
         </is>
       </c>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>モデル
+          <t>モデル1
 四色目の衣装・鞄</t>
         </is>
       </c>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>モデル、通行人
+          <t>モデル1、通行人
 四色ぶんの衣装・鞄</t>
         </is>
       </c>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>モデル
+          <t>モデル1
 鞄 四種類、ロゴ</t>
         </is>
       </c>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>モデル
+          <t>モデル2
 鞄、鉄のフェンス</t>
         </is>
       </c>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>モデル
+          <t>モデル2
 鞄、持ち物、靴、ロゴ</t>
         </is>
       </c>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>モデル
+          <t>モデル2
 鞄、中に入れる持ち物</t>
         </is>
       </c>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>モデル
+          <t>モデル2
 鞄</t>
         </is>
       </c>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>モデル鞄</t>
+          <t>モデル2鞄</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>一色目は仲通りの並木が奥まで抜ける位置。二色目は横断歩道を渡りきるところで、目の前を車が通り過ぎた一コマでつなぐ。信号待ちが入るので三十分取る。
+          <t>一色目は仲通りの並木が奥まで抜ける位置。二色目は横断歩道を渡りきるところで、目の前を車が通り過ぎた一コマでつなぐ。
 2カット</t>
         </is>
       </c>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>ガラス棟の扉（またいで中へ入る）</t>
+          <t>ガラス棟の扉</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -957,7 +957,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>出演者
+          <t>モデル1
 鞄、机</t>
         </is>
       </c>
@@ -992,7 +992,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>出演者
+          <t>モデル1
 A4書類、13インチPC</t>
         </is>
       </c>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>出演者
+          <t>モデル1
 手帳、鍵、サングラス、ペン、傘、水筒</t>
         </is>
       </c>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>出演者
+          <t>モデル1
 鞄</t>
         </is>
       </c>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>出演者と衣装・鞄 四色ぶんが揃ってから。永尾さんの車も要る（①の合図）。曇りの日に合わせる。晴れたら可変NDを付ける。予備日を一日とる。</t>
+          <t>モデル2（①）とモデル3（④）の二人。衣装・鞄 四色ぶんが揃ってから。永尾さんの車も要る（①の合図）。曇りの日に合わせる。晴れたら可変NDを付ける。予備日を一日とる。</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>モデル1
+          <t>モデル2
 一色目の衣装・鞄</t>
         </is>
       </c>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>モデル1
+          <t>モデル2
 二色目の衣装・鞄</t>
         </is>
       </c>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>モデル1
+          <t>モデル2
 三色目の衣装・鞄</t>
         </is>
       </c>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>モデル1
+          <t>モデル2
 四色目の衣装・鞄</t>
         </is>
       </c>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>モデル1、通行人
+          <t>モデル2、通行人
 四色ぶんの衣装・鞄</t>
         </is>
       </c>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>モデル1
+          <t>モデル2
 鞄 四種類、ロゴ</t>
         </is>
       </c>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>出演者の拘束は 9:00〜16:05。</t>
+          <t>モデル2の拘束は 9:00〜11:45。モデル3は 13:30〜16:05。</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>モデル2
+          <t>モデル3
 鞄、鉄のフェンス</t>
         </is>
       </c>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>モデル2
+          <t>モデル3
 鞄、持ち物、靴、ロゴ</t>
         </is>
       </c>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>モデル2
+          <t>モデル3
 鞄、中に入れる持ち物</t>
         </is>
       </c>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>モデルの手が真俯瞰で映る。鞄に入れる持ち物を先に並べておく。
+          <t>モデル3の手が真俯瞰で映る。鞄に入れる持ち物を先に並べておく。
 3カット</t>
         </is>
       </c>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>モデル2
+          <t>モデル3
 鞄</t>
         </is>
       </c>
@@ -3270,12 +3270,12 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>けやき並木の歩道（出演者はここまで）</t>
+          <t>けやき並木の歩道（モデル3はここまで）</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>モデル2鞄</t>
+          <t>モデル3鞄</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>人が映らないカット。モデルが帰ったあとでよい。
+          <t>人が映らないカット。モデル3が帰ったあとでよい。
 1カット</t>
         </is>
       </c>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>五日目</t>
+          <t>五日目　モデル2</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>五日目</t>
+          <t>五日目　モデル3</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>一日目</t>
+          <t>一日目　モデル1</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -3341,15 +3341,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3365,20 +3364,15 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>顔が映るか</t>
+          <t>当日の支度</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>当日の支度</t>
+          <t>衣装</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>衣装</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>そのほか</t>
         </is>
@@ -3397,22 +3391,17 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>映る（腰より上の寄りがある）</t>
+          <t>鏡だけ。四回の着替えのあと、髪の乱れを直す。</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>鏡だけ。四回の着替えのあと、髪の乱れを直す。</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>四色ぶんの服と鞄。鞄の色と喧嘩しない服を選ぶ。
 ヘアメイクを付けないので、髪型が崩れない服にする ──
 前開きの上着なら、着替えで髪が乱れない。</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>着替え場所と荷物置き場。四回の着替えを見込んで、
 東京国際フォーラムは使用時間を長めに申請する。</t>
@@ -3432,21 +3421,16 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>主役にしない（引きと後ろ姿）</t>
+          <t>爪を切りそろえる。手が寄りで映る。</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>爪を切りそろえる。手が寄りで映る。</t>
+          <t>一そろい。街に馴染む色。
+ベージュや白、グレーなどの色。</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>一そろい。街に馴染む色。
-鞄より目立つ柄は避ける。</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>時計・指輪は外す。
 歩く距離があるので、履き慣れた靴で。</t>
@@ -3466,22 +3450,17 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>映らない</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
           <t>爪を切り、手を洗っておく。
 時計・指輪は外す。</t>
         </is>
       </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>袖口の見える無地の上着。
+ベージュや白、グレーなどのカラー。</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>袖口の見える無地の上着。
-柄物だと、手の動きより袖に目が行く。</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>物を置く速さが一定にできる方を選ぶ。
 一度通してもらってから本番。</t>
@@ -3501,21 +3480,15 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>映る（バストショット）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>本人のふだんの服のみでOK。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>本人のふだんの服。
-細かい柄は画面で目がちらつくので避ける。</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>顔出しの範囲を、撮る前に本人へ確認する。
 名前は出さず「購入者Aさん」とだけ出す。
@@ -3536,21 +3509,16 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>映る（バストショット・横顔）</t>
+          <t>襟元と髪だけ、撮る直前に鏡で見る。</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>襟元と髪だけ、撮る直前に鏡で見る。</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>ふだんの仕事着。
 永尾社長・くさがやさんは一日目、佐藤さんは四日目。</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>永尾社長・佐藤さん・くさがやさん。
 三人とも三十分ずつ。</t>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>永尾社長、くさがやさん
+          <t>永尾社長、くさがやさん（または内藤さん・渡辺さん）
 色見本、革、店舗の机</t>
         </is>
       </c>
@@ -923,7 +923,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>永尾社長、くさがやさん
+          <t>永尾社長、くさがやさん（または内藤さん・渡辺さん）
 図面、型紙</t>
         </is>
       </c>

--- a/pdf/01_香盤表.xlsx
+++ b/pdf/01_香盤表.xlsx
@@ -8,11 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日程" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="一日目" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="二日目" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="三日目" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四日目" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="五日目" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1日目" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2日目" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3日目" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4日目" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5日目" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出演者と支度" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -517,7 +517,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>全八本 135カット ／ 撮影 五日 ／ 日付は10月中で未定</t>
+          <t>全八本 135カット ／ 撮影 5日 ／ 日付は10月中で未定</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>一日目</t>
+          <t>1日目</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="6" ht="75" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>二日目</t>
+          <t>2日目</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>三日目</t>
+          <t>3日目</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -636,7 +636,7 @@
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>四日目</t>
+          <t>4日目</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -665,7 +665,7 @@
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>五日目</t>
+          <t>5日目</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>一日目　── 10月中（日にちは未定・月曜か火曜）</t>
+          <t>1日目　── 10月中（日にちは未定・月曜か火曜）</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>二日目　── 10月中（日にちは未定・月曜か火曜）</t>
+          <t>2日目　── 10月中（日にちは未定・月曜か火曜）</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>手元の品が読める寄りは撮らない。四日目と同じ光の向き・高さ・距離、同じケルビンで組む。</t>
+          <t>手元の品が読める寄りは撮らない。4日目と同じ光の向き・高さ・距離、同じケルビンで組む。</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>五シーンとも、くさがやさんが頭から通して作る。工程は分けない。佐藤さんの二枚（S3 4枚目の目元・S5 1枚目の引き）だけ四日目に工房で撮る。
+          <t>五シーンとも、くさがやさんが頭から通して作る。工程は分けない。佐藤さんの二枚（S3 4枚目の目元・S5 1枚目の引き）だけ4日目に工房で撮る。
 2カット</t>
         </is>
       </c>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>3カット（4枚目は四日目に撮る）</t>
+          <t>3カット（4枚目は4日目に撮る）</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>4カット（1枚目は四日目に撮る）</t>
+          <t>4カット（1枚目は4日目に撮る）</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>三日目　── 10月中（日にちは未定・平日）</t>
+          <t>3日目　── 10月中（日にちは未定・平日）</t>
         </is>
       </c>
     </row>
@@ -1996,8 +1996,8 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>佐藤さんの引きだけは四日目に撮る。
-2カット（3枚目は四日目に撮る）</t>
+          <t>佐藤さんの引きだけは4日目に撮る。
+2カット（3枚目は4日目に撮る）</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       <c r="F17" s="5" t="inlineStr">
         <is>
           <t>紙とテープの音を拾う。
-2カット（3枚目は四日目に撮る）</t>
+2カット（3枚目は4日目に撮る）</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>四日目　── 10月中（日にちは未定・休日）</t>
+          <t>4日目　── 10月中（日にちは未定・休日）</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       <c r="F12" s="5" t="inlineStr">
         <is>
           <t>寄りと引きを交互に。
-2カット（2枚目・3枚目・4枚目は二日目に撮る）</t>
+2カット（2枚目・3枚目・4枚目は2日目に撮る）</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>二日目と同じ光の向き・高さ・距離・同じケルビンで組む。手も品も画に入れない。だから工程が切れない。</t>
+          <t>2日目と同じ光の向き・高さ・距離・同じケルビンで組む。手も品も画に入れない。だから工程が切れない。</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>五日目　── 10月中（日にちは未定）</t>
+          <t>5日目　── 10月中（日にちは未定）</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>五日目　モデル2</t>
+          <t>5日目　モデル2</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>五日目　モデル3</t>
+          <t>5日目　モデル3</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>一日目　モデル1</t>
+          <t>1日目　モデル1</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>二日目</t>
+          <t>2日目</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>一日目・四日目</t>
+          <t>1日目・4日目</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -3515,7 +3515,7 @@
       <c r="D6" s="5" t="inlineStr">
         <is>
           <t>ふだんの仕事着。
-永尾社長・くさがやさんは一日目、佐藤さんは四日目。</t>
+永尾社長・くさがやさんは1日目、佐藤さんは4日目。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
